--- a/data/trans_orig/P33_2_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P33_2_2023-Edad-trans_orig.xlsx
@@ -489,7 +489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de horas que duerme habitualmente al día durante los fines de semana</t>
+          <t>Número medio de horas que duerme habitualmente al día durante los fines de semana (tasa de respuesta: 97,11%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,96; 8,32</t>
+          <t>7,94; 8,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,82; 8,21</t>
+          <t>7,82; 8,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,95; 8,22</t>
+          <t>7,94; 8,21</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,53; 7,84</t>
+          <t>7,54; 7,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,31; 7,64</t>
+          <t>7,29; 7,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,45; 7,69</t>
+          <t>7,43; 7,7</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,28; 7,48</t>
+          <t>7,28; 7,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,31; 7,44</t>
+          <t>7,31; 7,45</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,2; 9,1</t>
+          <t>7,2; 9,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,21; 8,66</t>
+          <t>7,21; 8,58</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,07; 7,25</t>
+          <t>7,08; 7,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,99; 7,11</t>
+          <t>6,98; 7,11</t>
         </is>
       </c>
     </row>
@@ -821,17 +821,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,95; 7,15</t>
+          <t>6,94; 7,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,23; 6,97</t>
+          <t>6,28; 6,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,45; 7,02</t>
+          <t>6,42; 7,02</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,98; 7,22</t>
+          <t>6,99; 7,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,92; 7,08</t>
+          <t>6,91; 7,07</t>
         </is>
       </c>
     </row>
@@ -921,17 +921,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,37; 8,08</t>
+          <t>7,36; 8,13</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,96; 7,26</t>
+          <t>6,99; 7,26</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,26; 7,67</t>
+          <t>7,24; 7,72</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P33_2_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P33_2_2023-Edad-trans_orig.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>8,15</t>
+          <t>8,09</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8,09</t>
+          <t>8,05</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,94; 8,32</t>
+          <t>7,91; 8,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -581,7 +581,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,94; 8,21</t>
+          <t>7,92; 8,16</t>
         </is>
       </c>
     </row>
@@ -598,17 +598,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7,69</t>
+          <t>7,71</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7,5</t>
+          <t>7,58</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7,59</t>
+          <t>7,65</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,54; 7,84</t>
+          <t>7,56; 7,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,29; 7,64</t>
+          <t>7,46; 7,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,43; 7,7</t>
+          <t>7,56; 7,74</t>
         </is>
       </c>
     </row>
@@ -648,12 +648,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>7,38</t>
+          <t>7,4</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>7,38</t>
+          <t>7,36</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,28; 7,47</t>
+          <t>7,31; 7,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,3; 7,46</t>
+          <t>7,29; 7,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,31; 7,45</t>
+          <t>7,32; 7,44</t>
         </is>
       </c>
     </row>
@@ -698,17 +698,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>8,01</t>
+          <t>7,26</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>7,22</t>
+          <t>7,23</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7,66</t>
+          <t>7,24</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,2; 9,08</t>
+          <t>7,16; 7,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,15; 7,3</t>
+          <t>7,16; 7,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,21; 8,58</t>
+          <t>7,18; 7,3</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,08; 7,26</t>
+          <t>7,08; 7,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,98; 7,11</t>
+          <t>6,99; 7,1</t>
         </is>
       </c>
     </row>
@@ -798,17 +798,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>7,05</t>
+          <t>7,06</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>6,62</t>
+          <t>6,94</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6,78</t>
+          <t>7,0</t>
         </is>
       </c>
     </row>
@@ -821,17 +821,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,94; 7,15</t>
+          <t>6,96; 7,16</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,28; 6,97</t>
+          <t>6,85; 7,03</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,42; 7,02</t>
+          <t>6,93; 7,06</t>
         </is>
       </c>
     </row>
@@ -848,17 +848,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>7,1</t>
+          <t>7,11</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>6,93</t>
+          <t>6,95</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7,0</t>
+          <t>7,01</t>
         </is>
       </c>
     </row>
@@ -871,17 +871,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,99; 7,24</t>
+          <t>6,98; 7,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,83; 7,03</t>
+          <t>6,85; 7,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,91; 7,07</t>
+          <t>6,94; 7,09</t>
         </is>
       </c>
     </row>
@@ -898,17 +898,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>7,57</t>
+          <t>7,38</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7,17</t>
+          <t>7,26</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7,37</t>
+          <t>7,32</t>
         </is>
       </c>
     </row>
@@ -921,17 +921,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,36; 8,13</t>
+          <t>7,34; 7,43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,99; 7,26</t>
+          <t>7,22; 7,3</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,24; 7,72</t>
+          <t>7,29; 7,35</t>
         </is>
       </c>
     </row>
